--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487009_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487009_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4481</v>
+        <v>6.9937</v>
       </c>
       <c r="E2" t="n">
-        <v>6.412</v>
+        <v>5.4318</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0361</v>
+        <v>1.5618</v>
       </c>
       <c r="G2" t="n">
         <v>4.5291</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1325</v>
+        <v>0.678</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0381</v>
+        <v>0.0579</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0944</v>
+        <v>0.6201</v>
       </c>
       <c r="V2" t="n">
         <v>0.3491</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.395</v>
+        <v>5.9295</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0459</v>
+        <v>2.4915</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3491</v>
+        <v>3.438</v>
       </c>
       <c r="G3" t="n">
         <v>4.3059</v>
@@ -688,13 +688,13 @@
         <v>3.0801</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5722</v>
+        <v>-0.0377</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9804</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4082</v>
+        <v>0.4971</v>
       </c>
       <c r="V3" t="n">
         <v>-1.4189</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2546</v>
+        <v>5.1458</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5428</v>
+        <v>2.2562</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7117</v>
+        <v>2.8896</v>
       </c>
       <c r="G4" t="n">
         <v>0.0784</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5602</v>
+        <v>0.4513</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2826</v>
+        <v>-0.0041</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2776</v>
+        <v>0.4554</v>
       </c>
       <c r="V4" t="n">
         <v>2.3573</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1168</v>
+        <v>0.4281</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4595</v>
+        <v>-1.1185</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5763</v>
+        <v>1.5466</v>
       </c>
       <c r="G5" t="n">
         <v>0.4403</v>
@@ -844,13 +844,13 @@
         <v>3.0801</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0461</v>
+        <v>0.3574</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6782</v>
+        <v>-0.3373</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6947</v>
       </c>
       <c r="V5" t="n">
         <v>-1.3963</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0535</v>
+        <v>0.4049</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7685</v>
+        <v>0.7541</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.715</v>
+        <v>-0.3492</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0251</v>
+        <v>-1.387</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7883</v>
+        <v>-0.4345</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2368</v>
+        <v>-0.9525</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0334</v>
+        <v>0.3358</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.4545</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6445</v>
+        <v>-0.1188</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9917</v>
+        <v>-1.7228</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1104</v>
+        <v>-0.889</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8813</v>
+        <v>-0.8338</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.1143</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.1781</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.134</v>
+        <v>-0.0638</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5571</v>
+        <v>-0.1805</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1486</v>
+        <v>0.4159</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4085</v>
+        <v>-0.5964</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.387</v>
+        <v>-1.0251</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4345</v>
+        <v>-0.7883</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9525</v>
+        <v>-0.2368</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3358</v>
+        <v>-0.0334</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4545</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1188</v>
+        <v>0.6445</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7228</v>
+        <v>-0.9917</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.889</v>
+        <v>-0.1104</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8338</v>
+        <v>-0.8813</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8477</v>
+        <v>0.4339</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7246</v>
+        <v>0.4493</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1231</v>
+        <v>-0.0155</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.125</v>
+        <v>-0.4036</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9485</v>
+        <v>-0.4642</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1766</v>
+        <v>0.0606</v>
       </c>
       <c r="G8" t="n">
         <v>0.0459</v>
@@ -1078,13 +1078,13 @@
         <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4193</v>
+        <v>0.3021</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3489</v>
+        <v>0.1354</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0704</v>
+        <v>0.1667</v>
       </c>
       <c r="V8" t="n">
         <v>0.4805</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3239</v>
+        <v>-0.7005</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3766</v>
+        <v>-2.9311</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0527</v>
+        <v>2.2306</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3688</v>
@@ -1156,13 +1156,13 @@
         <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1953</v>
+        <v>0.4281</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5465</v>
+        <v>-0.1009</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3512</v>
+        <v>0.529</v>
       </c>
       <c r="V9" t="n">
         <v>0.2402</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6655</v>
+        <v>-1.5609</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9617</v>
+        <v>-0.8571</v>
       </c>
       <c r="F10" t="n">
         <v>-0.7038</v>
@@ -1234,10 +1234,10 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4843</v>
+        <v>0.5889</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2362</v>
+        <v>0.3409</v>
       </c>
       <c r="U10" t="n">
         <v>0.248</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2087</v>
+        <v>-2.1428</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0728</v>
+        <v>-0.0069</v>
       </c>
       <c r="F11" t="n">
         <v>-2.1359</v>
@@ -1312,10 +1312,10 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1317</v>
+        <v>-0.0659</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1317</v>
+        <v>-0.0659</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9248</v>
+        <v>-5.4626</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3203</v>
+        <v>-2.5023</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6045</v>
+        <v>-2.9602</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0123</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4715</v>
+        <v>0.9337</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6042</v>
+        <v>0.4222</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8672</v>
+        <v>0.5115</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3573</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.463</v>
+        <v>8.4511</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4812</v>
+        <v>3.4694</v>
       </c>
       <c r="F13" t="n">
-        <v>4.9816</v>
+        <v>4.9817</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6737999999999982</v>
@@ -1468,13 +1468,13 @@
         <v>18.4808</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1962</v>
+        <v>4.1841</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4473000000000001</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6434</v>
+        <v>3.6432</v>
       </c>
       <c r="V13" t="n">
         <v>-3.2731</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2313</v>
+        <v>2.9175</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4251</v>
+        <v>3.1113</v>
       </c>
       <c r="F14" t="n">
         <v>-0.1938</v>
@@ -1546,10 +1546,10 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4107</v>
+        <v>0.0969</v>
       </c>
       <c r="T14" t="n">
-        <v>0.244</v>
+        <v>-0.0698</v>
       </c>
       <c r="U14" t="n">
         <v>0.1667</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9807</v>
+        <v>2.8622</v>
       </c>
       <c r="E15" t="n">
         <v>2.7162</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2646</v>
+        <v>0.146</v>
       </c>
       <c r="G15" t="n">
         <v>0.699</v>
@@ -1624,13 +1624,13 @@
         <v>0.4107</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1031</v>
+        <v>-0.0155</v>
       </c>
       <c r="T15" t="n">
         <v>-0.124</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2271</v>
+        <v>0.1086</v>
       </c>
       <c r="V15" t="n">
         <v>1.7679</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0067</v>
+        <v>2.3642</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6468</v>
+        <v>1.856</v>
       </c>
       <c r="F16" t="n">
-        <v>0.36</v>
+        <v>0.5082</v>
       </c>
       <c r="G16" t="n">
         <v>2.0551</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6644</v>
+        <v>-0.307</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0077</v>
+        <v>0.2169</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6721</v>
+        <v>-0.5239</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9666</v>
+        <v>1.4339</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9986</v>
+        <v>1.2078</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.032</v>
+        <v>0.226</v>
       </c>
       <c r="G17" t="n">
         <v>3.0813</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4711</v>
+        <v>-0.0039</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.5504</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2884</v>
+        <v>0.5465</v>
       </c>
       <c r="V17" t="n">
         <v>0.8205</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4567</v>
+        <v>0.7007</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5191</v>
+        <v>-0.4145</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9758</v>
+        <v>1.1153</v>
       </c>
       <c r="G18" t="n">
         <v>0.43</v>
@@ -1858,13 +1858,13 @@
         <v>0.2053</v>
       </c>
       <c r="S18" t="n">
-        <v>0.124</v>
+        <v>0.3681</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2985</v>
+        <v>-0.1939</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4225</v>
+        <v>0.5619</v>
       </c>
       <c r="V18" t="n">
         <v>0.9294</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2246</v>
+        <v>0.6221</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3416</v>
+        <v>-0.7466</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.117</v>
+        <v>1.3687</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5633</v>
+        <v>1.6264</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5153</v>
+        <v>-0.8308</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0786</v>
+        <v>2.4572</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9565</v>
+        <v>1.3147</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7592</v>
+        <v>-0.4214</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1973</v>
+        <v>1.7361</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5198</v>
+        <v>0.3117</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2438</v>
+        <v>-0.4094</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2759</v>
+        <v>0.7211</v>
       </c>
       <c r="P19" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.753</v>
+        <v>-0.8988</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.159</v>
+        <v>-0.8293</v>
       </c>
       <c r="U19" t="n">
-        <v>0.912</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2402</v>
+        <v>0.0998</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3573</v>
+        <v>0.0998</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1421</v>
+        <v>0.2031</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3349</v>
+        <v>-0.1257</v>
       </c>
       <c r="F20" t="n">
-        <v>0.477</v>
+        <v>0.3288</v>
       </c>
       <c r="G20" t="n">
         <v>2.9839</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1642</v>
+        <v>-1.1032</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6587</v>
+        <v>-0.4495</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5054</v>
+        <v>-0.6536</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0363</v>
+        <v>-0.785</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9558</v>
+        <v>1.1324</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9921</v>
+        <v>-1.9174</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6264</v>
+        <v>-0.5633</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8308</v>
+        <v>0.5153</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4572</v>
+        <v>-1.0786</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3147</v>
+        <v>0.9565</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4214</v>
+        <v>0.7592</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7361</v>
+        <v>0.1973</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3117</v>
+        <v>-1.5198</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4094</v>
+        <v>-0.2438</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7211</v>
+        <v>-1.2759</v>
       </c>
       <c r="P21" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4846</v>
+        <v>-0.2566</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0385</v>
+        <v>-0.3682</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4461</v>
+        <v>0.1116</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0998</v>
+        <v>0.2402</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0998</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4859</v>
+        <v>-3.5033</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0752</v>
+        <v>-3.389</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4106</v>
+        <v>-0.1142</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4823</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0035</v>
+        <v>-1.0209</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3411</v>
+        <v>-0.655</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6624</v>
+        <v>-0.366</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.487</v>
+        <v>-3.9012</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3582</v>
+        <v>-3.149</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1289</v>
+        <v>-0.7523</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9473</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3766</v>
+        <v>0.2092</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5774</v>
+        <v>-0.3682</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2008</v>
+        <v>0.5774</v>
       </c>
       <c r="V23" t="n">
         <v>1.301</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.535</v>
+        <v>-9.6797</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8666</v>
+        <v>-7.1804</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6684</v>
+        <v>-2.4993</v>
       </c>
       <c r="G24" t="n">
         <v>-5.8325</v>
@@ -2326,13 +2326,13 @@
         <v>0.4107</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5776</v>
+        <v>0.4329</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0618</v>
+        <v>-0.252</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5158</v>
+        <v>0.6849</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4053</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4629</v>
+        <v>-6.765499999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9815</v>
+        <v>-4.981499999999997</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4812</v>
+        <v>-1.784</v>
       </c>
       <c r="G25" t="n">
         <v>0.6738</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9430999999999998</v>
+        <v>-0.9430999999999989</v>
       </c>
       <c r="I25" t="n">
         <v>1.6169</v>
@@ -2386,7 +2386,7 @@
         <v>5.667000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.304500000000001</v>
+        <v>-8.304499999999999</v>
       </c>
       <c r="N25" t="n">
         <v>-4.2545</v>
@@ -2404,13 +2404,13 @@
         <v>10.2671</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.195999999999999</v>
+        <v>-2.498799999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.6433</v>
+        <v>-3.6434</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4473</v>
+        <v>1.1446</v>
       </c>
       <c r="V25" t="n">
         <v>3.2731</v>
